--- a/moduli_aziende/aifecs/moduli_compilati/MOD-400-A-Contesto.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-400-A-Contesto.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R231d82381f3449a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5621b19d61774698"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -383,9 +366,7 @@
       <x:c r="G2" s="8" t="str">
         <x:v>DIR / SOC</x:v>
       </x:c>
-      <x:c r="H2" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H2" s="9"/>
     </x:row>
     <x:row r="3" ht="68" customHeight="1">
       <x:c r="A3" s="8" t="str">
@@ -407,9 +388,7 @@
       <x:c r="G3" s="8" t="str">
         <x:v>SOC / DID</x:v>
       </x:c>
-      <x:c r="H3" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H3" s="9"/>
     </x:row>
     <x:row r="4" ht="68" customHeight="1">
       <x:c r="A4" s="8" t="str">
@@ -431,9 +410,7 @@
       <x:c r="G4" s="8" t="str">
         <x:v>DIR / DID</x:v>
       </x:c>
-      <x:c r="H4" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H4" s="9"/>
     </x:row>
     <x:row r="5" ht="68" customHeight="1">
       <x:c r="A5" s="8" t="str">
@@ -455,9 +432,7 @@
       <x:c r="G5" s="8" t="str">
         <x:v>DID / QUAL</x:v>
       </x:c>
-      <x:c r="H5" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H5" s="9"/>
     </x:row>
     <x:row r="6" ht="68" customHeight="1">
       <x:c r="A6" s="8" t="str">
@@ -479,9 +454,7 @@
       <x:c r="G6" s="8" t="str">
         <x:v>DID / SOC</x:v>
       </x:c>
-      <x:c r="H6" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H6" s="9"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="8" t="str">
@@ -503,9 +476,7 @@
       <x:c r="G7" s="8" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="H7" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H7" s="9"/>
     </x:row>
     <x:row r="8" ht="50" customHeight="1">
       <x:c r="A8" s="8" t="str">
@@ -527,9 +498,7 @@
       <x:c r="G8" s="8" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H8" s="9"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="8" t="str">
@@ -551,9 +520,7 @@
       <x:c r="G9" s="8" t="str">
         <x:v>IT</x:v>
       </x:c>
-      <x:c r="H9" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H9" s="9"/>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
       <x:c r="A10" s="8" t="str">
@@ -575,9 +542,7 @@
       <x:c r="G10" s="8" t="str">
         <x:v>IT / TUT</x:v>
       </x:c>
-      <x:c r="H10" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H10" s="9"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="8" t="str">
@@ -599,9 +564,7 @@
       <x:c r="G11" s="8" t="str">
         <x:v>SEG / DID</x:v>
       </x:c>
-      <x:c r="H11" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H11" s="9"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="8" t="str">
@@ -623,9 +586,7 @@
       <x:c r="G12" s="8" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="H12" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H12" s="9"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="8" t="str">
@@ -647,9 +608,7 @@
       <x:c r="G13" s="8" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="H13" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H13" s="9"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="8" t="str">
@@ -671,9 +630,7 @@
       <x:c r="G14" s="8" t="str">
         <x:v>DIR / IT / SEG</x:v>
       </x:c>
-      <x:c r="H14" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H14" s="9"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="8" t="str">
@@ -695,9 +652,7 @@
       <x:c r="G15" s="8" t="str">
         <x:v>QUAL / DID</x:v>
       </x:c>
-      <x:c r="H15" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H15" s="9"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="8" t="str">
@@ -719,9 +674,7 @@
       <x:c r="G16" s="8" t="str">
         <x:v>CTR / DID</x:v>
       </x:c>
-      <x:c r="H16" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H16" s="9"/>
     </x:row>
     <x:row r="17" ht="68" customHeight="1">
       <x:c r="A17" s="8" t="str">
@@ -743,9 +696,7 @@
       <x:c r="G17" s="8" t="str">
         <x:v>AMM / IT / DID</x:v>
       </x:c>
-      <x:c r="H17" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H17" s="9"/>
     </x:row>
     <x:row r="18" ht="68" customHeight="1">
       <x:c r="A18" s="8" t="str">
@@ -767,9 +718,7 @@
       <x:c r="G18" s="8" t="str">
         <x:v>SOC</x:v>
       </x:c>
-      <x:c r="H18" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H18" s="9"/>
     </x:row>
     <x:row r="19" ht="68" customHeight="1">
       <x:c r="A19" s="8" t="str">
@@ -791,9 +740,7 @@
       <x:c r="G19" s="8" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="H19" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H19" s="9"/>
     </x:row>
     <x:row r="20" ht="68" customHeight="1">
       <x:c r="A20" s="8" t="str">
@@ -815,9 +762,7 @@
       <x:c r="G20" s="8" t="str">
         <x:v>DIR / SEG</x:v>
       </x:c>
-      <x:c r="H20" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H20" s="9"/>
     </x:row>
     <x:row r="21" ht="86" customHeight="1">
       <x:c r="A21" s="8" t="str">
@@ -839,9 +784,7 @@
       <x:c r="G21" s="8" t="str">
         <x:v>DIR / IT / CTR</x:v>
       </x:c>
-      <x:c r="H21" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H21" s="9"/>
     </x:row>
     <x:row r="22" ht="68" customHeight="1">
       <x:c r="A22" s="8" t="str">
@@ -863,9 +806,7 @@
       <x:c r="G22" s="8" t="str">
         <x:v>QUAL</x:v>
       </x:c>
-      <x:c r="H22" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H22" s="9"/>
     </x:row>
     <x:row r="23" ht="68" customHeight="1">
       <x:c r="A23" s="8" t="str">
@@ -887,9 +828,7 @@
       <x:c r="G23" s="8" t="str">
         <x:v>QUAL / SOC</x:v>
       </x:c>
-      <x:c r="H23" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="H23" s="9"/>
     </x:row>
     <x:row r="24" ht="33.95000076293945" customHeight="1">
       <x:c r="A24" s="2"/>
@@ -1203,6 +1142,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf73c7939efbe40a8"/>
 </x:worksheet>
 </file>